--- a/artfynd/A 953-2025 artfynd.xlsx
+++ b/artfynd/A 953-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122448591</v>
+        <v>122448343</v>
       </c>
       <c r="B2" t="n">
-        <v>92065</v>
+        <v>98197</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566782</v>
+        <v>566841</v>
       </c>
       <c r="R2" t="n">
-        <v>6417171</v>
+        <v>6417151</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122448242</v>
+        <v>122448387</v>
       </c>
       <c r="B3" t="n">
-        <v>98185</v>
+        <v>92077</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,35 +802,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566842</v>
+        <v>566746</v>
       </c>
       <c r="R3" t="n">
-        <v>6417125</v>
+        <v>6417208</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122448343</v>
+        <v>122448460</v>
       </c>
       <c r="B4" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,11 +933,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566841</v>
+        <v>566765</v>
       </c>
       <c r="R4" t="n">
-        <v>6417151</v>
+        <v>6417156</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122448227</v>
+        <v>122448242</v>
       </c>
       <c r="B5" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566819</v>
+        <v>566842</v>
       </c>
       <c r="R5" t="n">
-        <v>6417120</v>
+        <v>6417125</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122448166</v>
+        <v>122448227</v>
       </c>
       <c r="B6" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566824</v>
+        <v>566819</v>
       </c>
       <c r="R6" t="n">
-        <v>6417099</v>
+        <v>6417120</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122448745</v>
+        <v>122448399</v>
       </c>
       <c r="B7" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,7 +1266,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1277,14 +1281,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 961, Rössle, Odensvi16.12615, Sm</t>
+          <t>A 963, Rössle, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566766</v>
+        <v>566739</v>
       </c>
       <c r="R7" t="n">
-        <v>6417161</v>
+        <v>6417213</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122448399</v>
+        <v>122448183</v>
       </c>
       <c r="B8" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,11 +1381,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1396,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566739</v>
+        <v>566799</v>
       </c>
       <c r="R8" t="n">
-        <v>6417213</v>
+        <v>6417099</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122448423</v>
+        <v>122448442</v>
       </c>
       <c r="B9" t="n">
-        <v>90839</v>
+        <v>98197</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,38 +1471,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5321</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1510,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566735</v>
+        <v>566756</v>
       </c>
       <c r="R9" t="n">
-        <v>6417185</v>
+        <v>6417156</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,11 +1543,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-03</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På murken asplåga.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,10 +1570,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122448665</v>
+        <v>122448166</v>
       </c>
       <c r="B10" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566804</v>
+        <v>566824</v>
       </c>
       <c r="R10" t="n">
-        <v>6417139</v>
+        <v>6417099</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1689,10 +1681,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122448517</v>
+        <v>122448745</v>
       </c>
       <c r="B11" t="n">
-        <v>92065</v>
+        <v>98197</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1701,45 +1693,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 963, Rössle, Odensvi, Sm</t>
+          <t>A 961, Rössle, Odensvi16.12615, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566775</v>
+        <v>566766</v>
       </c>
       <c r="R11" t="n">
-        <v>6417159</v>
+        <v>6417161</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1799,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122448495</v>
+        <v>122448891</v>
       </c>
       <c r="B12" t="n">
-        <v>98185</v>
+        <v>92077</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,35 +1804,34 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1847,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566759</v>
+        <v>566817</v>
       </c>
       <c r="R12" t="n">
-        <v>6417167</v>
+        <v>6417171</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122448891</v>
+        <v>122448476</v>
       </c>
       <c r="B13" t="n">
-        <v>92065</v>
+        <v>92077</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1957,10 +1949,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566817</v>
+        <v>566755</v>
       </c>
       <c r="R13" t="n">
-        <v>6417171</v>
+        <v>6417158</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,10 +2012,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122448154</v>
+        <v>122448208</v>
       </c>
       <c r="B14" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,10 +2060,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566820</v>
+        <v>566815</v>
       </c>
       <c r="R14" t="n">
-        <v>6417108</v>
+        <v>6417142</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,10 +2123,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122448652</v>
+        <v>122448665</v>
       </c>
       <c r="B15" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566800</v>
+        <v>566804</v>
       </c>
       <c r="R15" t="n">
-        <v>6417158</v>
+        <v>6417139</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2242,10 +2234,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122448183</v>
+        <v>122448517</v>
       </c>
       <c r="B16" t="n">
-        <v>98185</v>
+        <v>92077</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2254,35 +2246,34 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2290,10 +2281,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566799</v>
+        <v>566775</v>
       </c>
       <c r="R16" t="n">
-        <v>6417099</v>
+        <v>6417159</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2353,10 +2344,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122448208</v>
+        <v>122448495</v>
       </c>
       <c r="B17" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2401,10 +2392,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566815</v>
+        <v>566759</v>
       </c>
       <c r="R17" t="n">
-        <v>6417142</v>
+        <v>6417167</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2464,10 +2455,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122448387</v>
+        <v>122448154</v>
       </c>
       <c r="B18" t="n">
-        <v>92065</v>
+        <v>98197</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2476,34 +2467,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2511,10 +2503,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566746</v>
+        <v>566820</v>
       </c>
       <c r="R18" t="n">
-        <v>6417208</v>
+        <v>6417108</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2574,10 +2566,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122448476</v>
+        <v>122448591</v>
       </c>
       <c r="B19" t="n">
-        <v>92065</v>
+        <v>92077</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2621,10 +2613,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566755</v>
+        <v>566782</v>
       </c>
       <c r="R19" t="n">
-        <v>6417158</v>
+        <v>6417171</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2684,10 +2676,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122448442</v>
+        <v>122448652</v>
       </c>
       <c r="B20" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2732,10 +2724,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566756</v>
+        <v>566800</v>
       </c>
       <c r="R20" t="n">
-        <v>6417156</v>
+        <v>6417158</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2795,10 +2787,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122448460</v>
+        <v>122448423</v>
       </c>
       <c r="B21" t="n">
-        <v>98185</v>
+        <v>90851</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2807,35 +2799,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2843,10 +2838,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566765</v>
+        <v>566735</v>
       </c>
       <c r="R21" t="n">
-        <v>6417156</v>
+        <v>6417185</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2879,6 +2874,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På murken asplåga.</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 953-2025 artfynd.xlsx
+++ b/artfynd/A 953-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122448343</v>
+        <v>122448591</v>
       </c>
       <c r="B2" t="n">
-        <v>98197</v>
+        <v>92082</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566841</v>
+        <v>566782</v>
       </c>
       <c r="R2" t="n">
-        <v>6417151</v>
+        <v>6417171</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122448387</v>
+        <v>122448208</v>
       </c>
       <c r="B3" t="n">
-        <v>92077</v>
+        <v>98202</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,34 +797,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566746</v>
+        <v>566815</v>
       </c>
       <c r="R3" t="n">
-        <v>6417208</v>
+        <v>6417142</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122448460</v>
+        <v>122448154</v>
       </c>
       <c r="B4" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566765</v>
+        <v>566820</v>
       </c>
       <c r="R4" t="n">
-        <v>6417156</v>
+        <v>6417108</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122448242</v>
+        <v>122448166</v>
       </c>
       <c r="B5" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566842</v>
+        <v>566824</v>
       </c>
       <c r="R5" t="n">
-        <v>6417125</v>
+        <v>6417099</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122448227</v>
+        <v>122448442</v>
       </c>
       <c r="B6" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566819</v>
+        <v>566756</v>
       </c>
       <c r="R6" t="n">
-        <v>6417120</v>
+        <v>6417156</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122448399</v>
+        <v>122448665</v>
       </c>
       <c r="B7" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,11 +1262,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1285,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566739</v>
+        <v>566804</v>
       </c>
       <c r="R7" t="n">
-        <v>6417213</v>
+        <v>6417139</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122448183</v>
+        <v>122448517</v>
       </c>
       <c r="B8" t="n">
-        <v>98197</v>
+        <v>92082</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,35 +1352,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1396,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566799</v>
+        <v>566775</v>
       </c>
       <c r="R8" t="n">
-        <v>6417099</v>
+        <v>6417159</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122448442</v>
+        <v>122448227</v>
       </c>
       <c r="B9" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1507,10 +1498,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566756</v>
+        <v>566819</v>
       </c>
       <c r="R9" t="n">
-        <v>6417156</v>
+        <v>6417120</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122448166</v>
+        <v>122448476</v>
       </c>
       <c r="B10" t="n">
-        <v>98197</v>
+        <v>92082</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1582,35 +1573,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1618,10 +1608,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566824</v>
+        <v>566755</v>
       </c>
       <c r="R10" t="n">
-        <v>6417099</v>
+        <v>6417158</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,10 +1671,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122448745</v>
+        <v>122448423</v>
       </c>
       <c r="B11" t="n">
-        <v>98197</v>
+        <v>90861</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1693,46 +1683,49 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 961, Rössle, Odensvi16.12615, Sm</t>
+          <t>A 963, Rössle, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566766</v>
+        <v>566735</v>
       </c>
       <c r="R11" t="n">
-        <v>6417161</v>
+        <v>6417185</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1765,6 +1758,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På murken asplåga.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1792,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122448891</v>
+        <v>122448745</v>
       </c>
       <c r="B12" t="n">
-        <v>92077</v>
+        <v>98202</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1804,45 +1802,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 963, Rössle, Odensvi, Sm</t>
+          <t>A 961, Rössle, Odensvi16.12615, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566817</v>
+        <v>566766</v>
       </c>
       <c r="R12" t="n">
-        <v>6417171</v>
+        <v>6417161</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,10 +1901,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122448476</v>
+        <v>122448387</v>
       </c>
       <c r="B13" t="n">
-        <v>92077</v>
+        <v>92082</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1949,10 +1948,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566755</v>
+        <v>566746</v>
       </c>
       <c r="R13" t="n">
-        <v>6417158</v>
+        <v>6417208</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,10 +2011,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122448208</v>
+        <v>122448242</v>
       </c>
       <c r="B14" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2060,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566815</v>
+        <v>566842</v>
       </c>
       <c r="R14" t="n">
-        <v>6417142</v>
+        <v>6417125</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2123,10 +2122,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122448665</v>
+        <v>122448183</v>
       </c>
       <c r="B15" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2171,10 +2170,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566804</v>
+        <v>566799</v>
       </c>
       <c r="R15" t="n">
-        <v>6417139</v>
+        <v>6417099</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2234,10 +2233,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122448517</v>
+        <v>122448460</v>
       </c>
       <c r="B16" t="n">
-        <v>92077</v>
+        <v>98202</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2246,34 +2245,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566775</v>
+        <v>566765</v>
       </c>
       <c r="R16" t="n">
-        <v>6417159</v>
+        <v>6417156</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122448495</v>
+        <v>122448343</v>
       </c>
       <c r="B17" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2377,7 +2377,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2392,10 +2396,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566759</v>
+        <v>566841</v>
       </c>
       <c r="R17" t="n">
-        <v>6417167</v>
+        <v>6417151</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2455,10 +2459,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122448154</v>
+        <v>122448891</v>
       </c>
       <c r="B18" t="n">
-        <v>98197</v>
+        <v>92082</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2467,35 +2471,34 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2503,10 +2506,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566820</v>
+        <v>566817</v>
       </c>
       <c r="R18" t="n">
-        <v>6417108</v>
+        <v>6417171</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2566,10 +2569,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122448591</v>
+        <v>122448399</v>
       </c>
       <c r="B19" t="n">
-        <v>92077</v>
+        <v>98202</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2578,34 +2581,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2613,10 +2621,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566782</v>
+        <v>566739</v>
       </c>
       <c r="R19" t="n">
-        <v>6417171</v>
+        <v>6417213</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2676,10 +2684,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122448652</v>
+        <v>122448495</v>
       </c>
       <c r="B20" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2724,10 +2732,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566800</v>
+        <v>566759</v>
       </c>
       <c r="R20" t="n">
-        <v>6417158</v>
+        <v>6417167</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2787,10 +2795,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122448423</v>
+        <v>122448652</v>
       </c>
       <c r="B21" t="n">
-        <v>90851</v>
+        <v>98202</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2799,38 +2807,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5321</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2838,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566735</v>
+        <v>566800</v>
       </c>
       <c r="R21" t="n">
-        <v>6417185</v>
+        <v>6417158</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2874,11 +2879,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-03</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På murken asplåga.</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 953-2025 artfynd.xlsx
+++ b/artfynd/A 953-2025 artfynd.xlsx
@@ -2233,10 +2233,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122448460</v>
+        <v>122448891</v>
       </c>
       <c r="B16" t="n">
-        <v>98202</v>
+        <v>92082</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2245,35 +2245,34 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2281,10 +2280,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566765</v>
+        <v>566817</v>
       </c>
       <c r="R16" t="n">
-        <v>6417156</v>
+        <v>6417171</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2344,7 +2343,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122448343</v>
+        <v>122448460</v>
       </c>
       <c r="B17" t="n">
         <v>98202</v>
@@ -2377,11 +2376,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2396,10 +2391,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566841</v>
+        <v>566765</v>
       </c>
       <c r="R17" t="n">
-        <v>6417151</v>
+        <v>6417156</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2459,10 +2454,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122448891</v>
+        <v>122448343</v>
       </c>
       <c r="B18" t="n">
-        <v>92082</v>
+        <v>98202</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2471,34 +2466,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566817</v>
+        <v>566841</v>
       </c>
       <c r="R18" t="n">
-        <v>6417171</v>
+        <v>6417151</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 953-2025 artfynd.xlsx
+++ b/artfynd/A 953-2025 artfynd.xlsx
@@ -1450,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122448227</v>
+        <v>122448476</v>
       </c>
       <c r="B9" t="n">
-        <v>98202</v>
+        <v>92082</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1462,35 +1462,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1498,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566819</v>
+        <v>566755</v>
       </c>
       <c r="R9" t="n">
-        <v>6417120</v>
+        <v>6417158</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,10 +1560,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122448476</v>
+        <v>122448227</v>
       </c>
       <c r="B10" t="n">
-        <v>92082</v>
+        <v>98202</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,34 +1572,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566755</v>
+        <v>566819</v>
       </c>
       <c r="R10" t="n">
-        <v>6417158</v>
+        <v>6417120</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 953-2025 artfynd.xlsx
+++ b/artfynd/A 953-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122448591</v>
+        <v>122448442</v>
       </c>
       <c r="B2" t="n">
-        <v>92082</v>
+        <v>98211</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566782</v>
+        <v>566756</v>
       </c>
       <c r="R2" t="n">
-        <v>6417171</v>
+        <v>6417156</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122448208</v>
+        <v>122448423</v>
       </c>
       <c r="B3" t="n">
-        <v>98202</v>
+        <v>90866</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,35 +793,33 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>5321</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566815</v>
+        <v>566735</v>
       </c>
       <c r="R3" t="n">
-        <v>6417142</v>
+        <v>6417185</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,6 +863,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På murken asplåga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122448154</v>
+        <v>122448517</v>
       </c>
       <c r="B4" t="n">
-        <v>98202</v>
+        <v>92087</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,35 +907,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>4364</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566820</v>
+        <v>566775</v>
       </c>
       <c r="R4" t="n">
-        <v>6417108</v>
+        <v>6417159</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122448166</v>
+        <v>122448745</v>
       </c>
       <c r="B5" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,11 +1017,6 @@
       </c>
       <c r="E5" t="n">
         <v>220787</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1051,14 +1039,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 963, Rössle, Odensvi, Sm</t>
+          <t>A 961, Rössle, Odensvi16.12615, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566824</v>
+        <v>566766</v>
       </c>
       <c r="R5" t="n">
-        <v>6417099</v>
+        <v>6417161</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122448442</v>
+        <v>122448652</v>
       </c>
       <c r="B6" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,11 +1123,6 @@
       </c>
       <c r="E6" t="n">
         <v>220787</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1166,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566756</v>
+        <v>566800</v>
       </c>
       <c r="R6" t="n">
-        <v>6417156</v>
+        <v>6417158</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122448665</v>
+        <v>122448154</v>
       </c>
       <c r="B7" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,11 +1229,6 @@
       </c>
       <c r="E7" t="n">
         <v>220787</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1277,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566804</v>
+        <v>566820</v>
       </c>
       <c r="R7" t="n">
-        <v>6417139</v>
+        <v>6417108</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,10 +1318,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122448517</v>
+        <v>122448591</v>
       </c>
       <c r="B8" t="n">
-        <v>92082</v>
+        <v>92087</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,11 +1335,6 @@
       </c>
       <c r="E8" t="n">
         <v>4364</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1387,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566775</v>
+        <v>566782</v>
       </c>
       <c r="R8" t="n">
-        <v>6417159</v>
+        <v>6417171</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122448476</v>
+        <v>122448208</v>
       </c>
       <c r="B9" t="n">
-        <v>92082</v>
+        <v>98211</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1462,34 +1435,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1497,10 +1466,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566755</v>
+        <v>566815</v>
       </c>
       <c r="R9" t="n">
-        <v>6417158</v>
+        <v>6417142</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1560,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122448227</v>
+        <v>122448387</v>
       </c>
       <c r="B10" t="n">
-        <v>98202</v>
+        <v>92087</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1572,35 +1541,29 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>4364</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1608,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566819</v>
+        <v>566746</v>
       </c>
       <c r="R10" t="n">
-        <v>6417120</v>
+        <v>6417208</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122448423</v>
+        <v>122448242</v>
       </c>
       <c r="B11" t="n">
-        <v>90861</v>
+        <v>98211</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1683,38 +1646,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5321</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Barkticka</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1722,10 +1677,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566735</v>
+        <v>566842</v>
       </c>
       <c r="R11" t="n">
-        <v>6417185</v>
+        <v>6417125</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,11 +1713,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-03</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På murken asplåga.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122448745</v>
+        <v>122448343</v>
       </c>
       <c r="B12" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1808,11 +1758,6 @@
       <c r="E12" t="n">
         <v>220787</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -1823,7 +1768,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1834,14 +1783,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 961, Rössle, Odensvi16.12615, Sm</t>
+          <t>A 963, Rössle, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566766</v>
+        <v>566841</v>
       </c>
       <c r="R12" t="n">
-        <v>6417161</v>
+        <v>6417151</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122448387</v>
+        <v>122448227</v>
       </c>
       <c r="B13" t="n">
-        <v>92082</v>
+        <v>98211</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1913,34 +1862,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1948,10 +1893,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566746</v>
+        <v>566819</v>
       </c>
       <c r="R13" t="n">
-        <v>6417208</v>
+        <v>6417120</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,10 +1956,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122448242</v>
+        <v>122448166</v>
       </c>
       <c r="B14" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2028,11 +1973,6 @@
       </c>
       <c r="E14" t="n">
         <v>220787</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2059,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566842</v>
+        <v>566824</v>
       </c>
       <c r="R14" t="n">
-        <v>6417125</v>
+        <v>6417099</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2122,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122448183</v>
+        <v>122448495</v>
       </c>
       <c r="B15" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2139,11 +2079,6 @@
       </c>
       <c r="E15" t="n">
         <v>220787</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2170,10 +2105,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566799</v>
+        <v>566759</v>
       </c>
       <c r="R15" t="n">
-        <v>6417099</v>
+        <v>6417167</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2233,10 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122448891</v>
+        <v>122448460</v>
       </c>
       <c r="B16" t="n">
-        <v>92082</v>
+        <v>98211</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2245,34 +2180,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2280,10 +2211,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566817</v>
+        <v>566765</v>
       </c>
       <c r="R16" t="n">
-        <v>6417171</v>
+        <v>6417156</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2343,10 +2274,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122448460</v>
+        <v>122448476</v>
       </c>
       <c r="B17" t="n">
-        <v>98202</v>
+        <v>92087</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2355,35 +2286,29 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>4364</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2391,10 +2316,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566765</v>
+        <v>566755</v>
       </c>
       <c r="R17" t="n">
-        <v>6417156</v>
+        <v>6417158</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,10 +2379,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122448343</v>
+        <v>122448399</v>
       </c>
       <c r="B18" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2472,11 +2397,6 @@
       <c r="E18" t="n">
         <v>220787</v>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -2489,7 +2409,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2506,10 +2426,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566841</v>
+        <v>566739</v>
       </c>
       <c r="R18" t="n">
-        <v>6417151</v>
+        <v>6417213</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2569,10 +2489,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122448399</v>
+        <v>122448665</v>
       </c>
       <c r="B19" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2587,11 +2507,6 @@
       <c r="E19" t="n">
         <v>220787</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -2602,11 +2517,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2621,10 +2532,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566739</v>
+        <v>566804</v>
       </c>
       <c r="R19" t="n">
-        <v>6417213</v>
+        <v>6417139</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2684,10 +2595,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122448495</v>
+        <v>122448891</v>
       </c>
       <c r="B20" t="n">
-        <v>98202</v>
+        <v>92087</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2696,35 +2607,29 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>4364</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2732,10 +2637,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566759</v>
+        <v>566817</v>
       </c>
       <c r="R20" t="n">
-        <v>6417167</v>
+        <v>6417171</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2795,10 +2700,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122448652</v>
+        <v>122448183</v>
       </c>
       <c r="B21" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2812,11 +2717,6 @@
       </c>
       <c r="E21" t="n">
         <v>220787</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2843,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566800</v>
+        <v>566799</v>
       </c>
       <c r="R21" t="n">
-        <v>6417158</v>
+        <v>6417099</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 953-2025 artfynd.xlsx
+++ b/artfynd/A 953-2025 artfynd.xlsx
@@ -2274,10 +2274,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122448476</v>
+        <v>122448399</v>
       </c>
       <c r="B17" t="n">
-        <v>92087</v>
+        <v>98211</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,29 +2286,34 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2316,10 +2321,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566755</v>
+        <v>566739</v>
       </c>
       <c r="R17" t="n">
-        <v>6417158</v>
+        <v>6417213</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2379,7 +2384,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122448399</v>
+        <v>122448665</v>
       </c>
       <c r="B18" t="n">
         <v>98211</v>
@@ -2407,11 +2412,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2426,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566739</v>
+        <v>566804</v>
       </c>
       <c r="R18" t="n">
-        <v>6417213</v>
+        <v>6417139</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2489,10 +2490,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122448665</v>
+        <v>122448476</v>
       </c>
       <c r="B19" t="n">
-        <v>98211</v>
+        <v>92087</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2501,30 +2502,29 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566804</v>
+        <v>566755</v>
       </c>
       <c r="R19" t="n">
-        <v>6417139</v>
+        <v>6417158</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 953-2025 artfynd.xlsx
+++ b/artfynd/A 953-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122448442</v>
+        <v>122448166</v>
       </c>
       <c r="B2" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>220787</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566756</v>
+        <v>566824</v>
       </c>
       <c r="R2" t="n">
-        <v>6417156</v>
+        <v>6417099</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122448423</v>
+        <v>122448460</v>
       </c>
       <c r="B3" t="n">
-        <v>90866</v>
+        <v>98224</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,33 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5321</v>
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -827,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566735</v>
+        <v>566765</v>
       </c>
       <c r="R3" t="n">
-        <v>6417185</v>
+        <v>6417156</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,11 +870,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På murken asplåga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122448517</v>
+        <v>122448423</v>
       </c>
       <c r="B4" t="n">
-        <v>92087</v>
+        <v>90879</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,22 +913,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5321</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -937,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566775</v>
+        <v>566735</v>
       </c>
       <c r="R4" t="n">
-        <v>6417159</v>
+        <v>6417185</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,6 +984,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På murken asplåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122448745</v>
+        <v>122448208</v>
       </c>
       <c r="B5" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,6 +1033,11 @@
       </c>
       <c r="E5" t="n">
         <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1039,14 +1060,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 961, Rössle, Odensvi16.12615, Sm</t>
+          <t>A 963, Rössle, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566766</v>
+        <v>566815</v>
       </c>
       <c r="R5" t="n">
-        <v>6417161</v>
+        <v>6417142</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122448652</v>
+        <v>122448442</v>
       </c>
       <c r="B6" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,6 +1144,11 @@
       </c>
       <c r="E6" t="n">
         <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1149,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566800</v>
+        <v>566756</v>
       </c>
       <c r="R6" t="n">
-        <v>6417158</v>
+        <v>6417156</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1241,7 @@
         <v>122448154</v>
       </c>
       <c r="B7" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,6 +1255,11 @@
       </c>
       <c r="E7" t="n">
         <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1321,7 +1352,7 @@
         <v>122448591</v>
       </c>
       <c r="B8" t="n">
-        <v>92087</v>
+        <v>92100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,6 +1366,11 @@
       </c>
       <c r="E8" t="n">
         <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1423,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122448208</v>
+        <v>122448891</v>
       </c>
       <c r="B9" t="n">
-        <v>98211</v>
+        <v>92100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,30 +1471,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1466,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566815</v>
+        <v>566817</v>
       </c>
       <c r="R9" t="n">
-        <v>6417142</v>
+        <v>6417171</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,10 +1569,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122448387</v>
+        <v>122448517</v>
       </c>
       <c r="B10" t="n">
-        <v>92087</v>
+        <v>92100</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,6 +1586,11 @@
       </c>
       <c r="E10" t="n">
         <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1571,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566746</v>
+        <v>566775</v>
       </c>
       <c r="R10" t="n">
-        <v>6417208</v>
+        <v>6417159</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1679,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122448242</v>
+        <v>122448495</v>
       </c>
       <c r="B11" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,6 +1696,11 @@
       </c>
       <c r="E11" t="n">
         <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1677,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566842</v>
+        <v>566759</v>
       </c>
       <c r="R11" t="n">
-        <v>6417125</v>
+        <v>6417167</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122448343</v>
+        <v>122448387</v>
       </c>
       <c r="B12" t="n">
-        <v>98211</v>
+        <v>92100</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,34 +1802,34 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1787,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566841</v>
+        <v>566746</v>
       </c>
       <c r="R12" t="n">
-        <v>6417151</v>
+        <v>6417208</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,10 +1900,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122448227</v>
+        <v>122448242</v>
       </c>
       <c r="B13" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1867,6 +1917,11 @@
       </c>
       <c r="E13" t="n">
         <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1893,10 +1948,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566819</v>
+        <v>566842</v>
       </c>
       <c r="R13" t="n">
-        <v>6417120</v>
+        <v>6417125</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,10 +2011,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122448166</v>
+        <v>122448652</v>
       </c>
       <c r="B14" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1973,6 +2028,11 @@
       </c>
       <c r="E14" t="n">
         <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1999,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566824</v>
+        <v>566800</v>
       </c>
       <c r="R14" t="n">
-        <v>6417099</v>
+        <v>6417158</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2062,10 +2122,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122448495</v>
+        <v>122448476</v>
       </c>
       <c r="B15" t="n">
-        <v>98211</v>
+        <v>92100</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2074,30 +2134,34 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4364</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2105,10 +2169,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566759</v>
+        <v>566755</v>
       </c>
       <c r="R15" t="n">
-        <v>6417167</v>
+        <v>6417158</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2168,10 +2232,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122448460</v>
+        <v>122448399</v>
       </c>
       <c r="B16" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2186,6 +2250,11 @@
       <c r="E16" t="n">
         <v>220787</v>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -2196,7 +2265,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2211,10 +2284,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566765</v>
+        <v>566739</v>
       </c>
       <c r="R16" t="n">
-        <v>6417156</v>
+        <v>6417213</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,10 +2347,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122448399</v>
+        <v>122448343</v>
       </c>
       <c r="B17" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2292,6 +2365,11 @@
       <c r="E17" t="n">
         <v>220787</v>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -2304,7 +2382,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2321,10 +2399,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566739</v>
+        <v>566841</v>
       </c>
       <c r="R17" t="n">
-        <v>6417213</v>
+        <v>6417151</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2384,10 +2462,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122448665</v>
+        <v>122448745</v>
       </c>
       <c r="B18" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2401,6 +2479,11 @@
       </c>
       <c r="E18" t="n">
         <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2423,14 +2506,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 963, Rössle, Odensvi, Sm</t>
+          <t>A 961, Rössle, Odensvi16.12615, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566804</v>
+        <v>566766</v>
       </c>
       <c r="R18" t="n">
-        <v>6417139</v>
+        <v>6417161</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2490,10 +2573,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122448476</v>
+        <v>122448183</v>
       </c>
       <c r="B19" t="n">
-        <v>92087</v>
+        <v>98224</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2502,29 +2585,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2532,10 +2621,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566755</v>
+        <v>566799</v>
       </c>
       <c r="R19" t="n">
-        <v>6417158</v>
+        <v>6417099</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2595,10 +2684,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122448891</v>
+        <v>122448665</v>
       </c>
       <c r="B20" t="n">
-        <v>92087</v>
+        <v>98224</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2607,29 +2696,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2637,10 +2732,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566817</v>
+        <v>566804</v>
       </c>
       <c r="R20" t="n">
-        <v>6417171</v>
+        <v>6417139</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2700,10 +2795,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122448183</v>
+        <v>122448227</v>
       </c>
       <c r="B21" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2717,6 +2812,11 @@
       </c>
       <c r="E21" t="n">
         <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2743,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566799</v>
+        <v>566819</v>
       </c>
       <c r="R21" t="n">
-        <v>6417099</v>
+        <v>6417120</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 953-2025 artfynd.xlsx
+++ b/artfynd/A 953-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122448166</v>
+        <v>122448891</v>
       </c>
       <c r="B2" t="n">
-        <v>98224</v>
+        <v>92113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566824</v>
+        <v>566817</v>
       </c>
       <c r="R2" t="n">
-        <v>6417099</v>
+        <v>6417171</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122448460</v>
+        <v>122448423</v>
       </c>
       <c r="B3" t="n">
-        <v>98224</v>
+        <v>90892</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +797,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566765</v>
+        <v>566735</v>
       </c>
       <c r="R3" t="n">
-        <v>6417156</v>
+        <v>6417185</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,6 +872,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På murken asplåga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122448423</v>
+        <v>122448166</v>
       </c>
       <c r="B4" t="n">
-        <v>90879</v>
+        <v>98237</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,38 +916,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5321</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566735</v>
+        <v>566824</v>
       </c>
       <c r="R4" t="n">
-        <v>6417185</v>
+        <v>6417099</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,11 +988,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På murken asplåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122448208</v>
+        <v>122448517</v>
       </c>
       <c r="B5" t="n">
-        <v>98224</v>
+        <v>92113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,35 +1027,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1064,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566815</v>
+        <v>566775</v>
       </c>
       <c r="R5" t="n">
-        <v>6417142</v>
+        <v>6417159</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122448442</v>
+        <v>122448665</v>
       </c>
       <c r="B6" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566756</v>
+        <v>566804</v>
       </c>
       <c r="R6" t="n">
-        <v>6417156</v>
+        <v>6417139</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122448154</v>
+        <v>122448208</v>
       </c>
       <c r="B7" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566820</v>
+        <v>566815</v>
       </c>
       <c r="R7" t="n">
-        <v>6417108</v>
+        <v>6417142</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122448591</v>
+        <v>122448387</v>
       </c>
       <c r="B8" t="n">
-        <v>92100</v>
+        <v>92113</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1396,10 +1394,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566782</v>
+        <v>566746</v>
       </c>
       <c r="R8" t="n">
-        <v>6417171</v>
+        <v>6417208</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122448891</v>
+        <v>122448745</v>
       </c>
       <c r="B9" t="n">
-        <v>92100</v>
+        <v>98237</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,45 +1469,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 963, Rössle, Odensvi, Sm</t>
+          <t>A 961, Rössle, Odensvi16.12615, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566817</v>
+        <v>566766</v>
       </c>
       <c r="R9" t="n">
-        <v>6417171</v>
+        <v>6417161</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122448517</v>
+        <v>122448460</v>
       </c>
       <c r="B10" t="n">
-        <v>92100</v>
+        <v>98237</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1581,34 +1580,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566775</v>
+        <v>566765</v>
       </c>
       <c r="R10" t="n">
-        <v>6417159</v>
+        <v>6417156</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,10 +1679,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122448495</v>
+        <v>122448591</v>
       </c>
       <c r="B11" t="n">
-        <v>98224</v>
+        <v>92113</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1691,35 +1691,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1727,10 +1726,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566759</v>
+        <v>566782</v>
       </c>
       <c r="R11" t="n">
-        <v>6417167</v>
+        <v>6417171</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1790,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122448387</v>
+        <v>122448652</v>
       </c>
       <c r="B12" t="n">
-        <v>92100</v>
+        <v>98237</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1802,34 +1801,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566746</v>
+        <v>566800</v>
       </c>
       <c r="R12" t="n">
-        <v>6417208</v>
+        <v>6417158</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,10 +1900,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122448242</v>
+        <v>122448183</v>
       </c>
       <c r="B13" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566842</v>
+        <v>566799</v>
       </c>
       <c r="R13" t="n">
-        <v>6417125</v>
+        <v>6417099</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,10 +2011,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122448652</v>
+        <v>122448242</v>
       </c>
       <c r="B14" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566800</v>
+        <v>566842</v>
       </c>
       <c r="R14" t="n">
-        <v>6417158</v>
+        <v>6417125</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2122,10 +2122,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122448476</v>
+        <v>122448399</v>
       </c>
       <c r="B15" t="n">
-        <v>92100</v>
+        <v>98237</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2134,34 +2134,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2169,10 +2174,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566755</v>
+        <v>566739</v>
       </c>
       <c r="R15" t="n">
-        <v>6417158</v>
+        <v>6417213</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,10 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122448399</v>
+        <v>122448495</v>
       </c>
       <c r="B16" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2265,11 +2270,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2284,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566739</v>
+        <v>566759</v>
       </c>
       <c r="R16" t="n">
-        <v>6417213</v>
+        <v>6417167</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2347,10 +2348,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122448343</v>
+        <v>122448476</v>
       </c>
       <c r="B17" t="n">
-        <v>98224</v>
+        <v>92113</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2359,39 +2360,34 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2399,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566841</v>
+        <v>566755</v>
       </c>
       <c r="R17" t="n">
-        <v>6417151</v>
+        <v>6417158</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2462,10 +2458,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122448745</v>
+        <v>122448343</v>
       </c>
       <c r="B18" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2495,7 +2491,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2506,14 +2506,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 961, Rössle, Odensvi16.12615, Sm</t>
+          <t>A 963, Rössle, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566766</v>
+        <v>566841</v>
       </c>
       <c r="R18" t="n">
-        <v>6417161</v>
+        <v>6417151</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2573,10 +2573,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122448183</v>
+        <v>122448227</v>
       </c>
       <c r="B19" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566799</v>
+        <v>566819</v>
       </c>
       <c r="R19" t="n">
-        <v>6417099</v>
+        <v>6417120</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2684,10 +2684,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122448665</v>
+        <v>122448442</v>
       </c>
       <c r="B20" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566804</v>
+        <v>566756</v>
       </c>
       <c r="R20" t="n">
-        <v>6417139</v>
+        <v>6417156</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122448227</v>
+        <v>122448154</v>
       </c>
       <c r="B21" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566819</v>
+        <v>566820</v>
       </c>
       <c r="R21" t="n">
-        <v>6417120</v>
+        <v>6417108</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 953-2025 artfynd.xlsx
+++ b/artfynd/A 953-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122448891</v>
+        <v>122448665</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>98237</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566817</v>
+        <v>566804</v>
       </c>
       <c r="R2" t="n">
-        <v>6417171</v>
+        <v>6417139</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122448423</v>
+        <v>122448495</v>
       </c>
       <c r="B3" t="n">
-        <v>90892</v>
+        <v>98237</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,38 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5321</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -836,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566735</v>
+        <v>566759</v>
       </c>
       <c r="R3" t="n">
-        <v>6417185</v>
+        <v>6417167</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,11 +870,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På murken asplåga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122448166</v>
+        <v>122448591</v>
       </c>
       <c r="B4" t="n">
-        <v>98237</v>
+        <v>92113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,35 +909,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -952,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566824</v>
+        <v>566782</v>
       </c>
       <c r="R4" t="n">
-        <v>6417099</v>
+        <v>6417171</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122448517</v>
+        <v>122448460</v>
       </c>
       <c r="B5" t="n">
-        <v>92113</v>
+        <v>98237</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1019,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1062,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566775</v>
+        <v>566765</v>
       </c>
       <c r="R5" t="n">
-        <v>6417159</v>
+        <v>6417156</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,7 +1118,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122448665</v>
+        <v>122448242</v>
       </c>
       <c r="B6" t="n">
         <v>98237</v>
@@ -1173,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566804</v>
+        <v>566842</v>
       </c>
       <c r="R6" t="n">
-        <v>6417139</v>
+        <v>6417125</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,7 +1229,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122448208</v>
+        <v>122448227</v>
       </c>
       <c r="B7" t="n">
         <v>98237</v>
@@ -1284,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566815</v>
+        <v>566819</v>
       </c>
       <c r="R7" t="n">
-        <v>6417142</v>
+        <v>6417120</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122448387</v>
+        <v>122448183</v>
       </c>
       <c r="B8" t="n">
-        <v>92113</v>
+        <v>98237</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,34 +1352,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1394,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566746</v>
+        <v>566799</v>
       </c>
       <c r="R8" t="n">
-        <v>6417208</v>
+        <v>6417099</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,7 +1451,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122448745</v>
+        <v>122448166</v>
       </c>
       <c r="B9" t="n">
         <v>98237</v>
@@ -1501,14 +1495,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 961, Rössle, Odensvi16.12615, Sm</t>
+          <t>A 963, Rössle, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566766</v>
+        <v>566824</v>
       </c>
       <c r="R9" t="n">
-        <v>6417161</v>
+        <v>6417099</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1562,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122448460</v>
+        <v>122448154</v>
       </c>
       <c r="B10" t="n">
         <v>98237</v>
@@ -1616,10 +1610,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566765</v>
+        <v>566820</v>
       </c>
       <c r="R10" t="n">
-        <v>6417156</v>
+        <v>6417108</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,7 +1673,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122448591</v>
+        <v>122448387</v>
       </c>
       <c r="B11" t="n">
         <v>92113</v>
@@ -1726,10 +1720,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566782</v>
+        <v>566746</v>
       </c>
       <c r="R11" t="n">
-        <v>6417171</v>
+        <v>6417208</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,7 +1783,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122448652</v>
+        <v>122448343</v>
       </c>
       <c r="B12" t="n">
         <v>98237</v>
@@ -1822,7 +1816,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1837,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566800</v>
+        <v>566841</v>
       </c>
       <c r="R12" t="n">
-        <v>6417158</v>
+        <v>6417151</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,7 +1898,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122448183</v>
+        <v>122448208</v>
       </c>
       <c r="B13" t="n">
         <v>98237</v>
@@ -1948,10 +1946,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566799</v>
+        <v>566815</v>
       </c>
       <c r="R13" t="n">
-        <v>6417099</v>
+        <v>6417142</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,10 +2009,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122448242</v>
+        <v>122448517</v>
       </c>
       <c r="B14" t="n">
-        <v>98237</v>
+        <v>92113</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2023,35 +2021,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2059,10 +2056,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566842</v>
+        <v>566775</v>
       </c>
       <c r="R14" t="n">
-        <v>6417125</v>
+        <v>6417159</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2122,10 +2119,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122448399</v>
+        <v>122448891</v>
       </c>
       <c r="B15" t="n">
-        <v>98237</v>
+        <v>92113</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2134,39 +2131,34 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2174,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566739</v>
+        <v>566817</v>
       </c>
       <c r="R15" t="n">
-        <v>6417213</v>
+        <v>6417171</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2237,10 +2229,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122448495</v>
+        <v>122448476</v>
       </c>
       <c r="B16" t="n">
-        <v>98237</v>
+        <v>92113</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2249,35 +2241,34 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2285,10 +2276,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566759</v>
+        <v>566755</v>
       </c>
       <c r="R16" t="n">
-        <v>6417167</v>
+        <v>6417158</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2348,10 +2339,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122448476</v>
+        <v>122448399</v>
       </c>
       <c r="B17" t="n">
-        <v>92113</v>
+        <v>98237</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2360,34 +2351,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2395,10 +2391,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566755</v>
+        <v>566739</v>
       </c>
       <c r="R17" t="n">
-        <v>6417158</v>
+        <v>6417213</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2458,7 +2454,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122448343</v>
+        <v>122448652</v>
       </c>
       <c r="B18" t="n">
         <v>98237</v>
@@ -2491,11 +2487,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2510,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566841</v>
+        <v>566800</v>
       </c>
       <c r="R18" t="n">
-        <v>6417151</v>
+        <v>6417158</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2573,7 +2565,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122448227</v>
+        <v>122448745</v>
       </c>
       <c r="B19" t="n">
         <v>98237</v>
@@ -2617,14 +2609,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A 963, Rössle, Odensvi, Sm</t>
+          <t>A 961, Rössle, Odensvi16.12615, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566819</v>
+        <v>566766</v>
       </c>
       <c r="R19" t="n">
-        <v>6417120</v>
+        <v>6417161</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2684,10 +2676,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122448442</v>
+        <v>122448423</v>
       </c>
       <c r="B20" t="n">
-        <v>98237</v>
+        <v>90892</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2696,35 +2688,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2732,10 +2727,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566756</v>
+        <v>566735</v>
       </c>
       <c r="R20" t="n">
-        <v>6417156</v>
+        <v>6417185</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2768,6 +2763,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På murken asplåga.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2795,7 +2795,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122448154</v>
+        <v>122448442</v>
       </c>
       <c r="B21" t="n">
         <v>98237</v>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566820</v>
+        <v>566756</v>
       </c>
       <c r="R21" t="n">
-        <v>6417108</v>
+        <v>6417156</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 953-2025 artfynd.xlsx
+++ b/artfynd/A 953-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122448665</v>
+        <v>122448891</v>
       </c>
       <c r="B2" t="n">
-        <v>98237</v>
+        <v>92114</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566804</v>
+        <v>566817</v>
       </c>
       <c r="R2" t="n">
-        <v>6417139</v>
+        <v>6417171</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122448495</v>
+        <v>122448652</v>
       </c>
       <c r="B3" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566759</v>
+        <v>566800</v>
       </c>
       <c r="R3" t="n">
-        <v>6417167</v>
+        <v>6417158</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122448591</v>
+        <v>122448227</v>
       </c>
       <c r="B4" t="n">
-        <v>92113</v>
+        <v>98240</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,34 +908,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566782</v>
+        <v>566819</v>
       </c>
       <c r="R4" t="n">
-        <v>6417171</v>
+        <v>6417120</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122448460</v>
+        <v>122448517</v>
       </c>
       <c r="B5" t="n">
-        <v>98237</v>
+        <v>92114</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,35 +1019,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1055,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566765</v>
+        <v>566775</v>
       </c>
       <c r="R5" t="n">
-        <v>6417156</v>
+        <v>6417159</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122448242</v>
+        <v>122448343</v>
       </c>
       <c r="B6" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,7 +1150,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1166,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566842</v>
+        <v>566841</v>
       </c>
       <c r="R6" t="n">
-        <v>6417125</v>
+        <v>6417151</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122448227</v>
+        <v>122448423</v>
       </c>
       <c r="B7" t="n">
-        <v>98237</v>
+        <v>90886</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,35 +1244,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1277,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566819</v>
+        <v>566735</v>
       </c>
       <c r="R7" t="n">
-        <v>6417120</v>
+        <v>6417185</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,6 +1319,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På murken asplåga.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122448183</v>
+        <v>122448399</v>
       </c>
       <c r="B8" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,7 +1384,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1388,10 +1403,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566799</v>
+        <v>566739</v>
       </c>
       <c r="R8" t="n">
-        <v>6417099</v>
+        <v>6417213</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122448166</v>
+        <v>122448665</v>
       </c>
       <c r="B9" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566824</v>
+        <v>566804</v>
       </c>
       <c r="R9" t="n">
-        <v>6417099</v>
+        <v>6417139</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,10 +1577,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122448154</v>
+        <v>122448166</v>
       </c>
       <c r="B10" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,10 +1625,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566820</v>
+        <v>566824</v>
       </c>
       <c r="R10" t="n">
-        <v>6417108</v>
+        <v>6417099</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1673,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122448387</v>
+        <v>122448476</v>
       </c>
       <c r="B11" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1720,10 +1735,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566746</v>
+        <v>566755</v>
       </c>
       <c r="R11" t="n">
-        <v>6417208</v>
+        <v>6417158</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,10 +1798,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122448343</v>
+        <v>122448495</v>
       </c>
       <c r="B12" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,11 +1831,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1835,10 +1846,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566841</v>
+        <v>566759</v>
       </c>
       <c r="R12" t="n">
-        <v>6417151</v>
+        <v>6417167</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1898,10 +1909,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122448208</v>
+        <v>122448460</v>
       </c>
       <c r="B13" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1946,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566815</v>
+        <v>566765</v>
       </c>
       <c r="R13" t="n">
-        <v>6417142</v>
+        <v>6417156</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2009,10 +2020,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122448517</v>
+        <v>122448745</v>
       </c>
       <c r="B14" t="n">
-        <v>92113</v>
+        <v>98240</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2021,45 +2032,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 963, Rössle, Odensvi, Sm</t>
+          <t>A 961, Rössle, Odensvi16.12615, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566775</v>
+        <v>566766</v>
       </c>
       <c r="R14" t="n">
-        <v>6417159</v>
+        <v>6417161</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2119,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122448891</v>
+        <v>122448591</v>
       </c>
       <c r="B15" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2166,7 +2178,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566817</v>
+        <v>566782</v>
       </c>
       <c r="R15" t="n">
         <v>6417171</v>
@@ -2229,10 +2241,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122448476</v>
+        <v>122448183</v>
       </c>
       <c r="B16" t="n">
-        <v>92113</v>
+        <v>98240</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2241,34 +2253,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2276,10 +2289,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566755</v>
+        <v>566799</v>
       </c>
       <c r="R16" t="n">
-        <v>6417158</v>
+        <v>6417099</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2339,10 +2352,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122448399</v>
+        <v>122448154</v>
       </c>
       <c r="B17" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2372,11 +2385,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2391,10 +2400,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566739</v>
+        <v>566820</v>
       </c>
       <c r="R17" t="n">
-        <v>6417213</v>
+        <v>6417108</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,10 +2463,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122448652</v>
+        <v>122448387</v>
       </c>
       <c r="B18" t="n">
-        <v>98237</v>
+        <v>92114</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2466,35 +2475,34 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2502,10 +2510,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566800</v>
+        <v>566746</v>
       </c>
       <c r="R18" t="n">
-        <v>6417158</v>
+        <v>6417208</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2565,10 +2573,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122448745</v>
+        <v>122448442</v>
       </c>
       <c r="B19" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2609,14 +2617,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A 961, Rössle, Odensvi16.12615, Sm</t>
+          <t>A 963, Rössle, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566766</v>
+        <v>566756</v>
       </c>
       <c r="R19" t="n">
-        <v>6417161</v>
+        <v>6417156</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2676,10 +2684,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122448423</v>
+        <v>122448242</v>
       </c>
       <c r="B20" t="n">
-        <v>90892</v>
+        <v>98240</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2688,38 +2696,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5321</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2727,10 +2732,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566735</v>
+        <v>566842</v>
       </c>
       <c r="R20" t="n">
-        <v>6417185</v>
+        <v>6417125</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2763,11 +2768,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-03</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På murken asplåga.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2795,10 +2795,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122448442</v>
+        <v>122448208</v>
       </c>
       <c r="B21" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566756</v>
+        <v>566815</v>
       </c>
       <c r="R21" t="n">
-        <v>6417156</v>
+        <v>6417142</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 953-2025 artfynd.xlsx
+++ b/artfynd/A 953-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122448891</v>
+        <v>122448387</v>
       </c>
       <c r="B2" t="n">
         <v>92114</v>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566817</v>
+        <v>566746</v>
       </c>
       <c r="R2" t="n">
-        <v>6417171</v>
+        <v>6417208</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122448652</v>
+        <v>122448442</v>
       </c>
       <c r="B3" t="n">
         <v>98240</v>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566800</v>
+        <v>566756</v>
       </c>
       <c r="R3" t="n">
-        <v>6417158</v>
+        <v>6417156</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,7 +896,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122448227</v>
+        <v>122448665</v>
       </c>
       <c r="B4" t="n">
         <v>98240</v>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566819</v>
+        <v>566804</v>
       </c>
       <c r="R4" t="n">
-        <v>6417120</v>
+        <v>6417139</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,7 +1007,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122448517</v>
+        <v>122448591</v>
       </c>
       <c r="B5" t="n">
         <v>92114</v>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566775</v>
+        <v>566782</v>
       </c>
       <c r="R5" t="n">
-        <v>6417159</v>
+        <v>6417171</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122448423</v>
+        <v>122448460</v>
       </c>
       <c r="B7" t="n">
-        <v>90886</v>
+        <v>98240</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,38 +1244,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5321</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1283,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566735</v>
+        <v>566765</v>
       </c>
       <c r="R7" t="n">
-        <v>6417185</v>
+        <v>6417156</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,11 +1316,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På murken asplåga.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,7 +1343,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122448399</v>
+        <v>122448242</v>
       </c>
       <c r="B8" t="n">
         <v>98240</v>
@@ -1384,11 +1376,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1403,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566739</v>
+        <v>566842</v>
       </c>
       <c r="R8" t="n">
-        <v>6417213</v>
+        <v>6417125</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1466,7 +1454,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122448665</v>
+        <v>122448183</v>
       </c>
       <c r="B9" t="n">
         <v>98240</v>
@@ -1514,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566804</v>
+        <v>566799</v>
       </c>
       <c r="R9" t="n">
-        <v>6417139</v>
+        <v>6417099</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,7 +1565,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122448166</v>
+        <v>122448399</v>
       </c>
       <c r="B10" t="n">
         <v>98240</v>
@@ -1610,7 +1598,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1625,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566824</v>
+        <v>566739</v>
       </c>
       <c r="R10" t="n">
-        <v>6417099</v>
+        <v>6417213</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,10 +1680,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122448476</v>
+        <v>122448745</v>
       </c>
       <c r="B11" t="n">
-        <v>92114</v>
+        <v>98240</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,45 +1692,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 963, Rössle, Odensvi, Sm</t>
+          <t>A 961, Rössle, Odensvi16.12615, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566755</v>
+        <v>566766</v>
       </c>
       <c r="R11" t="n">
-        <v>6417158</v>
+        <v>6417161</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1798,7 +1791,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122448495</v>
+        <v>122448227</v>
       </c>
       <c r="B12" t="n">
         <v>98240</v>
@@ -1846,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566759</v>
+        <v>566819</v>
       </c>
       <c r="R12" t="n">
-        <v>6417167</v>
+        <v>6417120</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1909,7 +1902,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122448460</v>
+        <v>122448208</v>
       </c>
       <c r="B13" t="n">
         <v>98240</v>
@@ -1957,10 +1950,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566765</v>
+        <v>566815</v>
       </c>
       <c r="R13" t="n">
-        <v>6417156</v>
+        <v>6417142</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,7 +2013,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122448745</v>
+        <v>122448652</v>
       </c>
       <c r="B14" t="n">
         <v>98240</v>
@@ -2064,14 +2057,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 961, Rössle, Odensvi16.12615, Sm</t>
+          <t>A 963, Rössle, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566766</v>
+        <v>566800</v>
       </c>
       <c r="R14" t="n">
-        <v>6417161</v>
+        <v>6417158</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,10 +2124,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122448591</v>
+        <v>122448166</v>
       </c>
       <c r="B15" t="n">
-        <v>92114</v>
+        <v>98240</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2143,34 +2136,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2178,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566782</v>
+        <v>566824</v>
       </c>
       <c r="R15" t="n">
-        <v>6417171</v>
+        <v>6417099</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2241,7 +2235,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122448183</v>
+        <v>122448154</v>
       </c>
       <c r="B16" t="n">
         <v>98240</v>
@@ -2289,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566799</v>
+        <v>566820</v>
       </c>
       <c r="R16" t="n">
-        <v>6417099</v>
+        <v>6417108</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2352,10 +2346,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122448154</v>
+        <v>122448423</v>
       </c>
       <c r="B17" t="n">
-        <v>98240</v>
+        <v>90886</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2364,35 +2358,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2400,10 +2397,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566820</v>
+        <v>566735</v>
       </c>
       <c r="R17" t="n">
-        <v>6417108</v>
+        <v>6417185</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2436,6 +2433,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På murken asplåga.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2463,7 +2465,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122448387</v>
+        <v>122448476</v>
       </c>
       <c r="B18" t="n">
         <v>92114</v>
@@ -2510,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566746</v>
+        <v>566755</v>
       </c>
       <c r="R18" t="n">
-        <v>6417208</v>
+        <v>6417158</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2573,10 +2575,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122448442</v>
+        <v>122448517</v>
       </c>
       <c r="B19" t="n">
-        <v>98240</v>
+        <v>92114</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2585,35 +2587,34 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2621,10 +2622,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566756</v>
+        <v>566775</v>
       </c>
       <c r="R19" t="n">
-        <v>6417156</v>
+        <v>6417159</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2684,10 +2685,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122448242</v>
+        <v>122448891</v>
       </c>
       <c r="B20" t="n">
-        <v>98240</v>
+        <v>92114</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2696,35 +2697,34 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566842</v>
+        <v>566817</v>
       </c>
       <c r="R20" t="n">
-        <v>6417125</v>
+        <v>6417171</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2795,7 +2795,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122448208</v>
+        <v>122448495</v>
       </c>
       <c r="B21" t="n">
         <v>98240</v>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566815</v>
+        <v>566759</v>
       </c>
       <c r="R21" t="n">
-        <v>6417142</v>
+        <v>6417167</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 953-2025 artfynd.xlsx
+++ b/artfynd/A 953-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122448387</v>
+        <v>122448745</v>
       </c>
       <c r="B2" t="n">
-        <v>92114</v>
+        <v>98241</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,45 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 963, Rössle, Odensvi, Sm</t>
+          <t>A 961, Rössle, Odensvi16.12615, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566746</v>
+        <v>566766</v>
       </c>
       <c r="R2" t="n">
-        <v>6417208</v>
+        <v>6417161</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122448442</v>
+        <v>122448891</v>
       </c>
       <c r="B3" t="n">
-        <v>98240</v>
+        <v>92115</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,35 +798,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566756</v>
+        <v>566817</v>
       </c>
       <c r="R3" t="n">
-        <v>6417156</v>
+        <v>6417171</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122448665</v>
+        <v>122448495</v>
       </c>
       <c r="B4" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566804</v>
+        <v>566759</v>
       </c>
       <c r="R4" t="n">
-        <v>6417139</v>
+        <v>6417167</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122448591</v>
+        <v>122448166</v>
       </c>
       <c r="B5" t="n">
-        <v>92114</v>
+        <v>98241</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,34 +1019,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566782</v>
+        <v>566824</v>
       </c>
       <c r="R5" t="n">
-        <v>6417171</v>
+        <v>6417099</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122448343</v>
+        <v>122448399</v>
       </c>
       <c r="B6" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,7 +1153,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1169,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566841</v>
+        <v>566739</v>
       </c>
       <c r="R6" t="n">
-        <v>6417151</v>
+        <v>6417213</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122448460</v>
+        <v>122448591</v>
       </c>
       <c r="B7" t="n">
-        <v>98240</v>
+        <v>92115</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,35 +1245,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566765</v>
+        <v>566782</v>
       </c>
       <c r="R7" t="n">
-        <v>6417156</v>
+        <v>6417171</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122448242</v>
+        <v>122448517</v>
       </c>
       <c r="B8" t="n">
-        <v>98240</v>
+        <v>92115</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,35 +1355,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1391,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566842</v>
+        <v>566775</v>
       </c>
       <c r="R8" t="n">
-        <v>6417125</v>
+        <v>6417159</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,7 +1456,7 @@
         <v>122448183</v>
       </c>
       <c r="B9" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1565,10 +1564,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122448399</v>
+        <v>122448387</v>
       </c>
       <c r="B10" t="n">
-        <v>98240</v>
+        <v>92115</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,39 +1576,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1617,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566739</v>
+        <v>566746</v>
       </c>
       <c r="R10" t="n">
-        <v>6417213</v>
+        <v>6417208</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122448745</v>
+        <v>122448242</v>
       </c>
       <c r="B11" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,14 +1718,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 961, Rössle, Odensvi16.12615, Sm</t>
+          <t>A 963, Rössle, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566766</v>
+        <v>566842</v>
       </c>
       <c r="R11" t="n">
-        <v>6417161</v>
+        <v>6417125</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122448227</v>
+        <v>122448652</v>
       </c>
       <c r="B12" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1839,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566819</v>
+        <v>566800</v>
       </c>
       <c r="R12" t="n">
-        <v>6417120</v>
+        <v>6417158</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122448208</v>
+        <v>122448442</v>
       </c>
       <c r="B13" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1950,10 +1944,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566815</v>
+        <v>566756</v>
       </c>
       <c r="R13" t="n">
-        <v>6417142</v>
+        <v>6417156</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122448652</v>
+        <v>122448208</v>
       </c>
       <c r="B14" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2061,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566800</v>
+        <v>566815</v>
       </c>
       <c r="R14" t="n">
-        <v>6417158</v>
+        <v>6417142</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,10 +2118,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122448166</v>
+        <v>122448227</v>
       </c>
       <c r="B15" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2172,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566824</v>
+        <v>566819</v>
       </c>
       <c r="R15" t="n">
-        <v>6417099</v>
+        <v>6417120</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,10 +2229,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122448154</v>
+        <v>122448343</v>
       </c>
       <c r="B16" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2268,7 +2262,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2283,10 +2281,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566820</v>
+        <v>566841</v>
       </c>
       <c r="R16" t="n">
-        <v>6417108</v>
+        <v>6417151</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,10 +2344,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122448423</v>
+        <v>122448460</v>
       </c>
       <c r="B17" t="n">
-        <v>90886</v>
+        <v>98241</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2358,38 +2356,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5321</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2397,10 +2392,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566735</v>
+        <v>566765</v>
       </c>
       <c r="R17" t="n">
-        <v>6417185</v>
+        <v>6417156</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2433,11 +2428,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-03</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På murken asplåga.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2465,10 +2455,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122448476</v>
+        <v>122448423</v>
       </c>
       <c r="B18" t="n">
-        <v>92114</v>
+        <v>90887</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2481,27 +2471,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>5321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2512,10 +2506,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566755</v>
+        <v>566735</v>
       </c>
       <c r="R18" t="n">
-        <v>6417158</v>
+        <v>6417185</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2548,6 +2542,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På murken asplåga.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2575,10 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122448517</v>
+        <v>122448476</v>
       </c>
       <c r="B19" t="n">
-        <v>92114</v>
+        <v>92115</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2622,10 +2621,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566775</v>
+        <v>566755</v>
       </c>
       <c r="R19" t="n">
-        <v>6417159</v>
+        <v>6417158</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2685,10 +2684,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122448891</v>
+        <v>122448154</v>
       </c>
       <c r="B20" t="n">
-        <v>92114</v>
+        <v>98241</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2697,34 +2696,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566817</v>
+        <v>566820</v>
       </c>
       <c r="R20" t="n">
-        <v>6417171</v>
+        <v>6417108</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122448495</v>
+        <v>122448665</v>
       </c>
       <c r="B21" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566759</v>
+        <v>566804</v>
       </c>
       <c r="R21" t="n">
-        <v>6417167</v>
+        <v>6417139</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 953-2025 artfynd.xlsx
+++ b/artfynd/A 953-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122448745</v>
+        <v>122448891</v>
       </c>
       <c r="B2" t="n">
-        <v>98241</v>
+        <v>92118</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 961, Rössle, Odensvi16.12615, Sm</t>
+          <t>A 963, Rössle, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566766</v>
+        <v>566817</v>
       </c>
       <c r="R2" t="n">
-        <v>6417161</v>
+        <v>6417171</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122448891</v>
+        <v>122448183</v>
       </c>
       <c r="B3" t="n">
-        <v>92115</v>
+        <v>98244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,34 +797,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566817</v>
+        <v>566799</v>
       </c>
       <c r="R3" t="n">
-        <v>6417171</v>
+        <v>6417099</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122448495</v>
+        <v>122448227</v>
       </c>
       <c r="B4" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566759</v>
+        <v>566819</v>
       </c>
       <c r="R4" t="n">
-        <v>6417167</v>
+        <v>6417120</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122448166</v>
+        <v>122448591</v>
       </c>
       <c r="B5" t="n">
-        <v>98241</v>
+        <v>92118</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,35 +1019,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1055,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566824</v>
+        <v>566782</v>
       </c>
       <c r="R5" t="n">
-        <v>6417099</v>
+        <v>6417171</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122448399</v>
+        <v>122448343</v>
       </c>
       <c r="B6" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,7 +1152,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1170,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566739</v>
+        <v>566841</v>
       </c>
       <c r="R6" t="n">
-        <v>6417213</v>
+        <v>6417151</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122448591</v>
+        <v>122448242</v>
       </c>
       <c r="B7" t="n">
-        <v>92115</v>
+        <v>98244</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,34 +1244,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566782</v>
+        <v>566842</v>
       </c>
       <c r="R7" t="n">
-        <v>6417171</v>
+        <v>6417125</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122448517</v>
+        <v>122448423</v>
       </c>
       <c r="B8" t="n">
-        <v>92115</v>
+        <v>90890</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,27 +1359,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>5321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1390,10 +1394,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566775</v>
+        <v>566735</v>
       </c>
       <c r="R8" t="n">
-        <v>6417159</v>
+        <v>6417185</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,6 +1430,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På murken asplåga.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,10 +1462,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122448183</v>
+        <v>122448399</v>
       </c>
       <c r="B9" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,7 +1495,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1501,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566799</v>
+        <v>566739</v>
       </c>
       <c r="R9" t="n">
-        <v>6417099</v>
+        <v>6417213</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,10 +1577,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122448387</v>
+        <v>122448495</v>
       </c>
       <c r="B10" t="n">
-        <v>92115</v>
+        <v>98244</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1576,34 +1589,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1611,10 +1625,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566746</v>
+        <v>566759</v>
       </c>
       <c r="R10" t="n">
-        <v>6417208</v>
+        <v>6417167</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122448242</v>
+        <v>122448154</v>
       </c>
       <c r="B11" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,10 +1736,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566842</v>
+        <v>566820</v>
       </c>
       <c r="R11" t="n">
-        <v>6417125</v>
+        <v>6417108</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,10 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122448652</v>
+        <v>122448665</v>
       </c>
       <c r="B12" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1833,10 +1847,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566800</v>
+        <v>566804</v>
       </c>
       <c r="R12" t="n">
-        <v>6417158</v>
+        <v>6417139</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,7 +1913,7 @@
         <v>122448442</v>
       </c>
       <c r="B13" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2010,7 +2024,7 @@
         <v>122448208</v>
       </c>
       <c r="B14" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2118,10 +2132,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122448227</v>
+        <v>122448517</v>
       </c>
       <c r="B15" t="n">
-        <v>98241</v>
+        <v>92118</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2130,35 +2144,34 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2166,10 +2179,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566819</v>
+        <v>566775</v>
       </c>
       <c r="R15" t="n">
-        <v>6417120</v>
+        <v>6417159</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2229,10 +2242,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122448343</v>
+        <v>122448652</v>
       </c>
       <c r="B16" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2262,11 +2275,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2281,10 +2290,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566841</v>
+        <v>566800</v>
       </c>
       <c r="R16" t="n">
-        <v>6417151</v>
+        <v>6417158</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2344,10 +2353,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122448460</v>
+        <v>122448745</v>
       </c>
       <c r="B17" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2388,14 +2397,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 963, Rössle, Odensvi, Sm</t>
+          <t>A 961, Rössle, Odensvi16.12615, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566765</v>
+        <v>566766</v>
       </c>
       <c r="R17" t="n">
-        <v>6417156</v>
+        <v>6417161</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2455,10 +2464,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122448423</v>
+        <v>122448476</v>
       </c>
       <c r="B18" t="n">
-        <v>90887</v>
+        <v>92118</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2471,31 +2480,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5321</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2506,10 +2511,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566735</v>
+        <v>566755</v>
       </c>
       <c r="R18" t="n">
-        <v>6417185</v>
+        <v>6417158</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2542,11 +2547,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-03</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På murken asplåga.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2574,10 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122448476</v>
+        <v>122448387</v>
       </c>
       <c r="B19" t="n">
-        <v>92115</v>
+        <v>92118</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566755</v>
+        <v>566746</v>
       </c>
       <c r="R19" t="n">
-        <v>6417158</v>
+        <v>6417208</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2684,10 +2684,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122448154</v>
+        <v>122448166</v>
       </c>
       <c r="B20" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566820</v>
+        <v>566824</v>
       </c>
       <c r="R20" t="n">
-        <v>6417108</v>
+        <v>6417099</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122448665</v>
+        <v>122448460</v>
       </c>
       <c r="B21" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566804</v>
+        <v>566765</v>
       </c>
       <c r="R21" t="n">
-        <v>6417139</v>
+        <v>6417156</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 953-2025 artfynd.xlsx
+++ b/artfynd/A 953-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122448891</v>
+        <v>122448227</v>
       </c>
       <c r="B2" t="n">
-        <v>92118</v>
+        <v>98244</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566817</v>
+        <v>566819</v>
       </c>
       <c r="R2" t="n">
-        <v>6417171</v>
+        <v>6417120</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122448183</v>
+        <v>122448460</v>
       </c>
       <c r="B3" t="n">
         <v>98244</v>
@@ -833,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566799</v>
+        <v>566765</v>
       </c>
       <c r="R3" t="n">
-        <v>6417099</v>
+        <v>6417156</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122448227</v>
+        <v>122448517</v>
       </c>
       <c r="B4" t="n">
-        <v>98244</v>
+        <v>92118</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,35 +909,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566819</v>
+        <v>566775</v>
       </c>
       <c r="R4" t="n">
-        <v>6417120</v>
+        <v>6417159</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,7 +1007,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122448591</v>
+        <v>122448476</v>
       </c>
       <c r="B5" t="n">
         <v>92118</v>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566782</v>
+        <v>566755</v>
       </c>
       <c r="R5" t="n">
-        <v>6417171</v>
+        <v>6417158</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,7 +1117,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122448343</v>
+        <v>122448242</v>
       </c>
       <c r="B6" t="n">
         <v>98244</v>
@@ -1150,11 +1150,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1169,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566841</v>
+        <v>566842</v>
       </c>
       <c r="R6" t="n">
-        <v>6417151</v>
+        <v>6417125</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122448242</v>
+        <v>122448591</v>
       </c>
       <c r="B7" t="n">
-        <v>98244</v>
+        <v>92118</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,35 +1240,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1280,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566842</v>
+        <v>566782</v>
       </c>
       <c r="R7" t="n">
-        <v>6417125</v>
+        <v>6417171</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,10 +1338,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122448423</v>
+        <v>122448399</v>
       </c>
       <c r="B8" t="n">
-        <v>90890</v>
+        <v>98244</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,38 +1350,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5321</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1394,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566735</v>
+        <v>566739</v>
       </c>
       <c r="R8" t="n">
-        <v>6417185</v>
+        <v>6417213</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,11 +1426,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-03</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På murken asplåga.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,7 +1453,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122448399</v>
+        <v>122448208</v>
       </c>
       <c r="B9" t="n">
         <v>98244</v>
@@ -1495,11 +1486,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1514,10 +1501,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566739</v>
+        <v>566815</v>
       </c>
       <c r="R9" t="n">
-        <v>6417213</v>
+        <v>6417142</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,7 +1564,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122448495</v>
+        <v>122448442</v>
       </c>
       <c r="B10" t="n">
         <v>98244</v>
@@ -1625,10 +1612,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566759</v>
+        <v>566756</v>
       </c>
       <c r="R10" t="n">
-        <v>6417167</v>
+        <v>6417156</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1799,7 +1786,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122448665</v>
+        <v>122448166</v>
       </c>
       <c r="B12" t="n">
         <v>98244</v>
@@ -1847,10 +1834,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566804</v>
+        <v>566824</v>
       </c>
       <c r="R12" t="n">
-        <v>6417139</v>
+        <v>6417099</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,7 +1897,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122448442</v>
+        <v>122448665</v>
       </c>
       <c r="B13" t="n">
         <v>98244</v>
@@ -1958,10 +1945,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566756</v>
+        <v>566804</v>
       </c>
       <c r="R13" t="n">
-        <v>6417156</v>
+        <v>6417139</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,7 +2008,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122448208</v>
+        <v>122448745</v>
       </c>
       <c r="B14" t="n">
         <v>98244</v>
@@ -2065,14 +2052,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 963, Rössle, Odensvi, Sm</t>
+          <t>A 961, Rössle, Odensvi16.12615, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566815</v>
+        <v>566766</v>
       </c>
       <c r="R14" t="n">
-        <v>6417142</v>
+        <v>6417161</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2132,7 +2119,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122448517</v>
+        <v>122448891</v>
       </c>
       <c r="B15" t="n">
         <v>92118</v>
@@ -2179,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566775</v>
+        <v>566817</v>
       </c>
       <c r="R15" t="n">
-        <v>6417159</v>
+        <v>6417171</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2242,7 +2229,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122448652</v>
+        <v>122448183</v>
       </c>
       <c r="B16" t="n">
         <v>98244</v>
@@ -2290,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566800</v>
+        <v>566799</v>
       </c>
       <c r="R16" t="n">
-        <v>6417158</v>
+        <v>6417099</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2353,10 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122448745</v>
+        <v>122448387</v>
       </c>
       <c r="B17" t="n">
-        <v>98244</v>
+        <v>92118</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2365,46 +2352,45 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 961, Rössle, Odensvi16.12615, Sm</t>
+          <t>A 963, Rössle, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566766</v>
+        <v>566746</v>
       </c>
       <c r="R17" t="n">
-        <v>6417161</v>
+        <v>6417208</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2464,10 +2450,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122448476</v>
+        <v>122448495</v>
       </c>
       <c r="B18" t="n">
-        <v>92118</v>
+        <v>98244</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2476,34 +2462,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2511,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566755</v>
+        <v>566759</v>
       </c>
       <c r="R18" t="n">
-        <v>6417158</v>
+        <v>6417167</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2574,10 +2561,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122448387</v>
+        <v>122448343</v>
       </c>
       <c r="B19" t="n">
-        <v>92118</v>
+        <v>98244</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2586,34 +2573,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2621,10 +2613,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566746</v>
+        <v>566841</v>
       </c>
       <c r="R19" t="n">
-        <v>6417208</v>
+        <v>6417151</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2684,10 +2676,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122448166</v>
+        <v>122448423</v>
       </c>
       <c r="B20" t="n">
-        <v>98244</v>
+        <v>90890</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2696,35 +2688,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2732,10 +2727,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566824</v>
+        <v>566735</v>
       </c>
       <c r="R20" t="n">
-        <v>6417099</v>
+        <v>6417185</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2768,6 +2763,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På murken asplåga.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2795,7 +2795,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122448460</v>
+        <v>122448652</v>
       </c>
       <c r="B21" t="n">
         <v>98244</v>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566765</v>
+        <v>566800</v>
       </c>
       <c r="R21" t="n">
-        <v>6417156</v>
+        <v>6417158</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 953-2025 artfynd.xlsx
+++ b/artfynd/A 953-2025 artfynd.xlsx
@@ -1007,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122448476</v>
+        <v>122448242</v>
       </c>
       <c r="B5" t="n">
-        <v>92118</v>
+        <v>98244</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,34 +1019,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566755</v>
+        <v>566842</v>
       </c>
       <c r="R5" t="n">
-        <v>6417158</v>
+        <v>6417125</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122448242</v>
+        <v>122448476</v>
       </c>
       <c r="B6" t="n">
-        <v>98244</v>
+        <v>92118</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,35 +1130,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566842</v>
+        <v>566755</v>
       </c>
       <c r="R6" t="n">
-        <v>6417125</v>
+        <v>6417158</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 953-2025 artfynd.xlsx
+++ b/artfynd/A 953-2025 artfynd.xlsx
@@ -1007,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122448242</v>
+        <v>122448476</v>
       </c>
       <c r="B5" t="n">
-        <v>98244</v>
+        <v>92118</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,35 +1019,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1055,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566842</v>
+        <v>566755</v>
       </c>
       <c r="R5" t="n">
-        <v>6417125</v>
+        <v>6417158</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122448476</v>
+        <v>122448242</v>
       </c>
       <c r="B6" t="n">
-        <v>92118</v>
+        <v>98244</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,34 +1129,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566755</v>
+        <v>566842</v>
       </c>
       <c r="R6" t="n">
-        <v>6417158</v>
+        <v>6417125</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 953-2025 artfynd.xlsx
+++ b/artfynd/A 953-2025 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122448460</v>
+        <v>122448517</v>
       </c>
       <c r="B3" t="n">
-        <v>98244</v>
+        <v>92118</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +798,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566765</v>
+        <v>566775</v>
       </c>
       <c r="R3" t="n">
-        <v>6417156</v>
+        <v>6417159</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122448517</v>
+        <v>122448460</v>
       </c>
       <c r="B4" t="n">
-        <v>92118</v>
+        <v>98244</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,34 +908,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566775</v>
+        <v>566765</v>
       </c>
       <c r="R4" t="n">
-        <v>6417159</v>
+        <v>6417156</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122448476</v>
+        <v>122448242</v>
       </c>
       <c r="B5" t="n">
-        <v>92118</v>
+        <v>98244</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,34 +1019,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566755</v>
+        <v>566842</v>
       </c>
       <c r="R5" t="n">
-        <v>6417158</v>
+        <v>6417125</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122448242</v>
+        <v>122448476</v>
       </c>
       <c r="B6" t="n">
-        <v>98244</v>
+        <v>92118</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,35 +1130,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566842</v>
+        <v>566755</v>
       </c>
       <c r="R6" t="n">
-        <v>6417125</v>
+        <v>6417158</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 953-2025 artfynd.xlsx
+++ b/artfynd/A 953-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122448227</v>
+        <v>122448891</v>
       </c>
       <c r="B2" t="n">
-        <v>98244</v>
+        <v>92221</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566819</v>
+        <v>566817</v>
       </c>
       <c r="R2" t="n">
-        <v>6417120</v>
+        <v>6417171</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122448517</v>
+        <v>122448166</v>
       </c>
       <c r="B3" t="n">
-        <v>92118</v>
+        <v>98347</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,34 +797,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566775</v>
+        <v>566824</v>
       </c>
       <c r="R3" t="n">
-        <v>6417159</v>
+        <v>6417099</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122448460</v>
+        <v>122448423</v>
       </c>
       <c r="B4" t="n">
-        <v>98244</v>
+        <v>90993</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,35 +908,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566765</v>
+        <v>566735</v>
       </c>
       <c r="R4" t="n">
-        <v>6417156</v>
+        <v>6417185</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,6 +983,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På murken asplåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122448242</v>
+        <v>122448460</v>
       </c>
       <c r="B5" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566842</v>
+        <v>566765</v>
       </c>
       <c r="R5" t="n">
-        <v>6417125</v>
+        <v>6417156</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122448476</v>
+        <v>122448343</v>
       </c>
       <c r="B6" t="n">
-        <v>92118</v>
+        <v>98347</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,34 +1138,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1165,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566755</v>
+        <v>566841</v>
       </c>
       <c r="R6" t="n">
-        <v>6417158</v>
+        <v>6417151</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122448591</v>
+        <v>122448399</v>
       </c>
       <c r="B7" t="n">
-        <v>92118</v>
+        <v>98347</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,34 +1253,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1275,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566782</v>
+        <v>566739</v>
       </c>
       <c r="R7" t="n">
-        <v>6417171</v>
+        <v>6417213</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122448399</v>
+        <v>122448745</v>
       </c>
       <c r="B8" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,11 +1389,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1386,14 +1400,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 963, Rössle, Odensvi, Sm</t>
+          <t>A 961, Rössle, Odensvi16.12615, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566739</v>
+        <v>566766</v>
       </c>
       <c r="R8" t="n">
-        <v>6417213</v>
+        <v>6417161</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,7 +1470,7 @@
         <v>122448208</v>
       </c>
       <c r="B9" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1567,7 +1581,7 @@
         <v>122448442</v>
       </c>
       <c r="B10" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1675,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122448154</v>
+        <v>122448476</v>
       </c>
       <c r="B11" t="n">
-        <v>98244</v>
+        <v>92221</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1687,35 +1701,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1723,10 +1736,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566820</v>
+        <v>566755</v>
       </c>
       <c r="R11" t="n">
-        <v>6417108</v>
+        <v>6417158</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,10 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122448166</v>
+        <v>122448183</v>
       </c>
       <c r="B12" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1834,7 +1847,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566824</v>
+        <v>566799</v>
       </c>
       <c r="R12" t="n">
         <v>6417099</v>
@@ -1897,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122448665</v>
+        <v>122448591</v>
       </c>
       <c r="B13" t="n">
-        <v>98244</v>
+        <v>92221</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1909,35 +1922,34 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1945,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566804</v>
+        <v>566782</v>
       </c>
       <c r="R13" t="n">
-        <v>6417139</v>
+        <v>6417171</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2008,10 +2020,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122448745</v>
+        <v>122448665</v>
       </c>
       <c r="B14" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2052,14 +2064,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 961, Rössle, Odensvi16.12615, Sm</t>
+          <t>A 963, Rössle, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566766</v>
+        <v>566804</v>
       </c>
       <c r="R14" t="n">
-        <v>6417161</v>
+        <v>6417139</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2119,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122448891</v>
+        <v>122448227</v>
       </c>
       <c r="B15" t="n">
-        <v>92118</v>
+        <v>98347</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2131,34 +2143,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2166,10 +2179,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566817</v>
+        <v>566819</v>
       </c>
       <c r="R15" t="n">
-        <v>6417171</v>
+        <v>6417120</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2229,10 +2242,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122448183</v>
+        <v>122448495</v>
       </c>
       <c r="B16" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2277,10 +2290,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566799</v>
+        <v>566759</v>
       </c>
       <c r="R16" t="n">
-        <v>6417099</v>
+        <v>6417167</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2343,7 +2356,7 @@
         <v>122448387</v>
       </c>
       <c r="B17" t="n">
-        <v>92118</v>
+        <v>92221</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2450,10 +2463,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122448495</v>
+        <v>122448154</v>
       </c>
       <c r="B18" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2498,10 +2511,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566759</v>
+        <v>566820</v>
       </c>
       <c r="R18" t="n">
-        <v>6417167</v>
+        <v>6417108</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2561,10 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122448343</v>
+        <v>122448242</v>
       </c>
       <c r="B19" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2594,11 +2607,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2613,10 +2622,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566841</v>
+        <v>566842</v>
       </c>
       <c r="R19" t="n">
-        <v>6417151</v>
+        <v>6417125</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2676,10 +2685,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122448423</v>
+        <v>122448517</v>
       </c>
       <c r="B20" t="n">
-        <v>90890</v>
+        <v>92221</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2692,31 +2701,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5321</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2727,10 +2732,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566735</v>
+        <v>566775</v>
       </c>
       <c r="R20" t="n">
-        <v>6417185</v>
+        <v>6417159</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2763,11 +2768,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-03</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På murken asplåga.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2798,7 +2798,7 @@
         <v>122448652</v>
       </c>
       <c r="B21" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 953-2025 artfynd.xlsx
+++ b/artfynd/A 953-2025 artfynd.xlsx
@@ -2020,7 +2020,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122448665</v>
+        <v>122448227</v>
       </c>
       <c r="B14" t="n">
         <v>98347</v>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566804</v>
+        <v>566819</v>
       </c>
       <c r="R14" t="n">
-        <v>6417139</v>
+        <v>6417120</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,7 +2131,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122448227</v>
+        <v>122448665</v>
       </c>
       <c r="B15" t="n">
         <v>98347</v>
@@ -2179,10 +2179,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566819</v>
+        <v>566804</v>
       </c>
       <c r="R15" t="n">
-        <v>6417120</v>
+        <v>6417139</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 953-2025 artfynd.xlsx
+++ b/artfynd/A 953-2025 artfynd.xlsx
@@ -1689,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122448476</v>
+        <v>122448183</v>
       </c>
       <c r="B11" t="n">
-        <v>92221</v>
+        <v>98347</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1701,34 +1701,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1736,10 +1737,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566755</v>
+        <v>566799</v>
       </c>
       <c r="R11" t="n">
-        <v>6417158</v>
+        <v>6417099</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1799,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122448183</v>
+        <v>122448476</v>
       </c>
       <c r="B12" t="n">
-        <v>98347</v>
+        <v>92221</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,35 +1812,34 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566799</v>
+        <v>566755</v>
       </c>
       <c r="R12" t="n">
-        <v>6417099</v>
+        <v>6417158</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 953-2025 artfynd.xlsx
+++ b/artfynd/A 953-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122448891</v>
+        <v>122448227</v>
       </c>
       <c r="B2" t="n">
-        <v>92221</v>
+        <v>98355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566817</v>
+        <v>566819</v>
       </c>
       <c r="R2" t="n">
-        <v>6417171</v>
+        <v>6417120</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122448166</v>
+        <v>122448517</v>
       </c>
       <c r="B3" t="n">
-        <v>98347</v>
+        <v>92225</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,35 +798,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566824</v>
+        <v>566775</v>
       </c>
       <c r="R3" t="n">
-        <v>6417099</v>
+        <v>6417159</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122448423</v>
+        <v>122448208</v>
       </c>
       <c r="B4" t="n">
-        <v>90993</v>
+        <v>98355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,38 +908,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5321</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566735</v>
+        <v>566815</v>
       </c>
       <c r="R4" t="n">
-        <v>6417185</v>
+        <v>6417142</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,11 +980,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På murken asplåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122448460</v>
+        <v>122448476</v>
       </c>
       <c r="B5" t="n">
-        <v>98347</v>
+        <v>92225</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,35 +1019,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1063,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566765</v>
+        <v>566755</v>
       </c>
       <c r="R5" t="n">
-        <v>6417156</v>
+        <v>6417158</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122448343</v>
+        <v>122448387</v>
       </c>
       <c r="B6" t="n">
-        <v>98347</v>
+        <v>92225</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,39 +1129,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1178,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566841</v>
+        <v>566746</v>
       </c>
       <c r="R6" t="n">
-        <v>6417151</v>
+        <v>6417208</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1241,10 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122448399</v>
+        <v>122448183</v>
       </c>
       <c r="B7" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,11 +1260,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1293,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566739</v>
+        <v>566799</v>
       </c>
       <c r="R7" t="n">
-        <v>6417213</v>
+        <v>6417099</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1356,10 +1338,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122448745</v>
+        <v>122448242</v>
       </c>
       <c r="B8" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1400,14 +1382,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 961, Rössle, Odensvi16.12615, Sm</t>
+          <t>A 963, Rössle, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566766</v>
+        <v>566842</v>
       </c>
       <c r="R8" t="n">
-        <v>6417161</v>
+        <v>6417125</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1467,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122448208</v>
+        <v>122448423</v>
       </c>
       <c r="B9" t="n">
-        <v>98347</v>
+        <v>90997</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,35 +1461,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1515,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566815</v>
+        <v>566735</v>
       </c>
       <c r="R9" t="n">
-        <v>6417142</v>
+        <v>6417185</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,6 +1536,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På murken asplåga.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122448442</v>
+        <v>122448154</v>
       </c>
       <c r="B10" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566756</v>
+        <v>566820</v>
       </c>
       <c r="R10" t="n">
-        <v>6417156</v>
+        <v>6417108</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1689,10 +1679,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122448183</v>
+        <v>122448665</v>
       </c>
       <c r="B11" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1737,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566799</v>
+        <v>566804</v>
       </c>
       <c r="R11" t="n">
-        <v>6417099</v>
+        <v>6417139</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122448476</v>
+        <v>122448891</v>
       </c>
       <c r="B12" t="n">
-        <v>92221</v>
+        <v>92225</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1847,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566755</v>
+        <v>566817</v>
       </c>
       <c r="R12" t="n">
-        <v>6417158</v>
+        <v>6417171</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,10 +1900,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122448591</v>
+        <v>122448399</v>
       </c>
       <c r="B13" t="n">
-        <v>92221</v>
+        <v>98355</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1922,34 +1912,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1957,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566782</v>
+        <v>566739</v>
       </c>
       <c r="R13" t="n">
-        <v>6417171</v>
+        <v>6417213</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,10 +2015,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122448227</v>
+        <v>122448745</v>
       </c>
       <c r="B14" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,14 +2059,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 963, Rössle, Odensvi, Sm</t>
+          <t>A 961, Rössle, Odensvi16.12615, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566819</v>
+        <v>566766</v>
       </c>
       <c r="R14" t="n">
-        <v>6417120</v>
+        <v>6417161</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122448665</v>
+        <v>122448652</v>
       </c>
       <c r="B15" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,10 +2174,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566804</v>
+        <v>566800</v>
       </c>
       <c r="R15" t="n">
-        <v>6417139</v>
+        <v>6417158</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2242,10 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122448495</v>
+        <v>122448166</v>
       </c>
       <c r="B16" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2290,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566759</v>
+        <v>566824</v>
       </c>
       <c r="R16" t="n">
-        <v>6417167</v>
+        <v>6417099</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2353,10 +2348,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122448387</v>
+        <v>122448343</v>
       </c>
       <c r="B17" t="n">
-        <v>92221</v>
+        <v>98355</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2365,34 +2360,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2400,10 +2400,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566746</v>
+        <v>566841</v>
       </c>
       <c r="R17" t="n">
-        <v>6417208</v>
+        <v>6417151</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2463,10 +2463,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122448154</v>
+        <v>122448495</v>
       </c>
       <c r="B18" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566820</v>
+        <v>566759</v>
       </c>
       <c r="R18" t="n">
-        <v>6417108</v>
+        <v>6417167</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2574,10 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122448242</v>
+        <v>122448442</v>
       </c>
       <c r="B19" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2622,10 +2622,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566842</v>
+        <v>566756</v>
       </c>
       <c r="R19" t="n">
-        <v>6417125</v>
+        <v>6417156</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2685,10 +2685,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122448517</v>
+        <v>122448460</v>
       </c>
       <c r="B20" t="n">
-        <v>92221</v>
+        <v>98355</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2697,34 +2697,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2732,10 +2733,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566775</v>
+        <v>566765</v>
       </c>
       <c r="R20" t="n">
-        <v>6417159</v>
+        <v>6417156</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2795,10 +2796,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122448652</v>
+        <v>122448591</v>
       </c>
       <c r="B21" t="n">
-        <v>98347</v>
+        <v>92225</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2807,35 +2808,34 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566800</v>
+        <v>566782</v>
       </c>
       <c r="R21" t="n">
-        <v>6417158</v>
+        <v>6417171</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
